--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,365 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120141847</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>338147</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433678</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120141657</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>338153</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6433685</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120141319</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91859</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brödtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum versipelle</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>338174</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva, Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>103418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R2" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B3" t="n">
-        <v>103418</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,9 +829,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R3" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +887,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141847</v>
+        <v>120141657</v>
       </c>
       <c r="B5" t="n">
         <v>96175</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338147</v>
+        <v>338153</v>
       </c>
       <c r="R5" t="n">
-        <v>6433678</v>
+        <v>6433685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,11 +1127,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B6" t="n">
-        <v>96175</v>
+        <v>91859</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,31 +1156,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R6" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141319</v>
+        <v>120173139</v>
       </c>
       <c r="B7" t="n">
-        <v>91859</v>
+        <v>96175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,45 +1276,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338174</v>
+        <v>338044</v>
       </c>
       <c r="R7" t="n">
-        <v>6433694</v>
+        <v>6433666</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,17 +1346,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,23 +1364,840 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120173172</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Intakan, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>337854</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6433652</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120173153</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Intakan, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>338039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6433662</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120173334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Intakan, sydväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>337690</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6433678</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Torrträd med spillkråkehack.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120173217</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105564</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Intakan, sydväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>337356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6433614</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120173236</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105564</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Intakan, sydväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>337280</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433628</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120173335</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Intakan, sydväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>337690</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433678</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120141847</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ale Skår 2:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>338147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433678</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Grimhild Angertuva</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B2" t="n">
-        <v>103418</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R2" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>103418</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,13 +832,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R3" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B5" t="n">
-        <v>96175</v>
+        <v>91859</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,31 +1039,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R5" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141319</v>
+        <v>120141657</v>
       </c>
       <c r="B6" t="n">
-        <v>91859</v>
+        <v>96175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338174</v>
+        <v>338153</v>
       </c>
       <c r="R6" t="n">
-        <v>6433694</v>
+        <v>6433685</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173139</v>
+        <v>120173153</v>
       </c>
       <c r="B7" t="n">
-        <v>96175</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,35 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338044</v>
+        <v>338039</v>
       </c>
       <c r="R7" t="n">
-        <v>6433666</v>
+        <v>6433662</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,6 +1351,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173172</v>
+        <v>120173236</v>
       </c>
       <c r="B8" t="n">
-        <v>57679</v>
+        <v>105564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,49 +1395,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337854</v>
+        <v>337280</v>
       </c>
       <c r="R8" t="n">
-        <v>6433652</v>
+        <v>6433628</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,7 +1475,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,6 +1484,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1494,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173153</v>
+        <v>120173335</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>96175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1519,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1534,21 +1543,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338039</v>
+        <v>337690</v>
       </c>
       <c r="R9" t="n">
-        <v>6433662</v>
+        <v>6433678</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1581,11 +1591,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173334</v>
+        <v>120173172</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>57679</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,20 +1630,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1646,24 +1651,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337690</v>
+        <v>337854</v>
       </c>
       <c r="R10" t="n">
-        <v>6433678</v>
+        <v>6433652</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Torrträd med spillkråkehack.</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,62 +1853,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173236</v>
+        <v>120141847</v>
       </c>
       <c r="B12" t="n">
-        <v>105564</v>
+        <v>96175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337280</v>
+        <v>338147</v>
       </c>
       <c r="R12" t="n">
-        <v>6433628</v>
+        <v>6433678</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1926,17 +1927,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,25 +1950,35 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173335</v>
+        <v>120173334</v>
       </c>
       <c r="B13" t="n">
-        <v>96175</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,39 +1987,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2054,13 +2057,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Torrträd med spillkråkehack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2079,14 +2086,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120141847</v>
+        <v>120173139</v>
       </c>
       <c r="B14" t="n">
         <v>96175</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2112,21 +2119,29 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338147</v>
+        <v>338044</v>
       </c>
       <c r="R14" t="n">
-        <v>6433678</v>
+        <v>6433666</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2153,17 +2168,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,28 +2186,135 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120222585</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94681</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Intakan, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>337818</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433625</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2316,6 +2316,715 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120259576</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Intakan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>338216</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433731</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120259582</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Intakan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>338165</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433704</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120259567</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Intakan, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>338072</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433703</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120259579</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96175</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Intakan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>338315</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433736</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växte 2 m norr om det ena diket.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120259558</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91859</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brödtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum versipelle</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Intakan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>338175</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433695</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120259571</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56282</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Intakan. öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>338098</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433731</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3025,6 +3025,567 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120338571</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>338470</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433759</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120329695</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>338256</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433688</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120329674</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>338302</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433745</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120338581</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>338444</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433736</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Allmänt spridd i sumdråg i området</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120329487</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>338473</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433748</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>103441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R2" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B3" t="n">
-        <v>103418</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,9 +829,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R3" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +887,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,7 +913,7 @@
         <v>119979131</v>
       </c>
       <c r="B4" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141319</v>
+        <v>120141657</v>
       </c>
       <c r="B5" t="n">
-        <v>91859</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1039,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338174</v>
+        <v>338153</v>
       </c>
       <c r="R5" t="n">
-        <v>6433694</v>
+        <v>6433685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,17 +1101,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,17 +1137,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B6" t="n">
-        <v>96175</v>
+        <v>91877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,31 +1156,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R6" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173153</v>
+        <v>120173139</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,34 +1280,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338039</v>
+        <v>338044</v>
       </c>
       <c r="R7" t="n">
-        <v>6433662</v>
+        <v>6433666</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,11 +1352,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,62 +1379,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173236</v>
+        <v>120141847</v>
       </c>
       <c r="B8" t="n">
-        <v>105564</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337280</v>
+        <v>338147</v>
       </c>
       <c r="R8" t="n">
-        <v>6433628</v>
+        <v>6433678</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,17 +1453,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,25 +1476,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173335</v>
+        <v>120173217</v>
       </c>
       <c r="B9" t="n">
-        <v>96175</v>
+        <v>105588</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,35 +1513,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1555,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337690</v>
+        <v>337356</v>
       </c>
       <c r="R9" t="n">
-        <v>6433678</v>
+        <v>6433614</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,6 +1589,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173172</v>
+        <v>120173334</v>
       </c>
       <c r="B10" t="n">
-        <v>57679</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,20 +1633,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,28 +1654,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337854</v>
+        <v>337690</v>
       </c>
       <c r="R10" t="n">
-        <v>6433652</v>
+        <v>6433678</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,7 +1705,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173217</v>
+        <v>120173153</v>
       </c>
       <c r="B11" t="n">
-        <v>105564</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,50 +1744,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>337356</v>
+        <v>338039</v>
       </c>
       <c r="R11" t="n">
-        <v>6433614</v>
+        <v>6433662</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1825,7 +1823,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,54 +1851,62 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120141847</v>
+        <v>120173236</v>
       </c>
       <c r="B12" t="n">
-        <v>96175</v>
+        <v>105588</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338147</v>
+        <v>337280</v>
       </c>
       <c r="R12" t="n">
-        <v>6433678</v>
+        <v>6433628</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1927,17 +1933,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,35 +1956,25 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173334</v>
+        <v>120173335</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,31 +1983,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2057,17 +2061,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Torrträd med spillkråkehack.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173139</v>
+        <v>120173172</v>
       </c>
       <c r="B14" t="n">
-        <v>96175</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,35 +2102,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2138,13 +2134,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338044</v>
+        <v>337854</v>
       </c>
       <c r="R14" t="n">
-        <v>6433666</v>
+        <v>6433652</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2176,13 +2172,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>120222585</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259576</v>
+        <v>120259582</v>
       </c>
       <c r="B16" t="n">
-        <v>57679</v>
+        <v>96198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,27 +2334,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2362,13 +2370,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338216</v>
+        <v>338165</v>
       </c>
       <c r="R16" t="n">
-        <v>6433731</v>
+        <v>6433704</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2400,17 +2408,13 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ingick i ett litet meståg.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259582</v>
+        <v>120259571</v>
       </c>
       <c r="B17" t="n">
-        <v>96175</v>
+        <v>56292</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,21 +2449,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100088</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2469,22 +2473,31 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338165</v>
+        <v>338098</v>
       </c>
       <c r="R17" t="n">
-        <v>6433704</v>
+        <v>6433731</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2517,6 +2530,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259567</v>
+        <v>120259579</v>
       </c>
       <c r="B18" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,7 +2597,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2592,14 +2610,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338072</v>
+        <v>338315</v>
       </c>
       <c r="R18" t="n">
-        <v>6433703</v>
+        <v>6433736</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2632,6 +2650,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259579</v>
+        <v>120259558</v>
       </c>
       <c r="B19" t="n">
-        <v>96175</v>
+        <v>91877</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,39 +2694,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2711,10 +2733,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338315</v>
+        <v>338175</v>
       </c>
       <c r="R19" t="n">
-        <v>6433736</v>
+        <v>6433695</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2751,7 +2773,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Växte 2 m norr om det ena diket.</t>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,10 +2801,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259558</v>
+        <v>120259567</v>
       </c>
       <c r="B20" t="n">
-        <v>91859</v>
+        <v>96198</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,49 +2813,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338175</v>
+        <v>338072</v>
       </c>
       <c r="R20" t="n">
-        <v>6433695</v>
+        <v>6433703</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,11 +2889,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259571</v>
+        <v>120259576</v>
       </c>
       <c r="B21" t="n">
-        <v>56282</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,16 +2932,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100088</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,41 +2949,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338098</v>
+        <v>338216</v>
       </c>
       <c r="R21" t="n">
         <v>6433731</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2999,7 +3000,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+          <t>Ingick i ett litet meståg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,7 +3009,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120338571</v>
+        <v>120338581</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,31 +3039,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338470</v>
+        <v>338444</v>
       </c>
       <c r="R22" t="n">
-        <v>6433759</v>
+        <v>6433736</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,6 +3120,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3138,7 +3139,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120329695</v>
+        <v>120338571</v>
       </c>
       <c r="B23" t="n">
         <v>57336</v>
@@ -3182,10 +3183,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338256</v>
+        <v>338470</v>
       </c>
       <c r="R23" t="n">
-        <v>6433688</v>
+        <v>6433759</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3223,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,16 +3234,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3365,10 +3356,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120338581</v>
+        <v>120329695</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,31 +3368,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3409,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338444</v>
+        <v>338256</v>
       </c>
       <c r="R25" t="n">
-        <v>6433736</v>
+        <v>6433688</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3449,7 +3440,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Allmänt spridd i sumdråg i området</t>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,9 +3449,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,6 +3586,358 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120391007</v>
+      </c>
+      <c r="B27" t="n">
+        <v>94344</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skår 1, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>337877</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433714</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120388441</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>338129</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 födosökande i tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120388500</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96877</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>338062</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433699</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Nära vägen, uppe på klippa.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B2" t="n">
-        <v>103441</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R2" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>103441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,13 +832,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R3" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173139</v>
+        <v>120173153</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,35 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1316,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338044</v>
+        <v>338039</v>
       </c>
       <c r="R7" t="n">
-        <v>6433666</v>
+        <v>6433662</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,6 +1351,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,51 +1383,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120141847</v>
+        <v>120173334</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338147</v>
+        <v>337690</v>
       </c>
       <c r="R8" t="n">
         <v>6433678</v>
@@ -1453,17 +1457,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,91 +1476,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173217</v>
+        <v>120141847</v>
       </c>
       <c r="B9" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337356</v>
+        <v>338147</v>
       </c>
       <c r="R9" t="n">
-        <v>6433614</v>
+        <v>6433678</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,17 +1568,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,25 +1591,35 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173334</v>
+        <v>120173172</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,20 +1628,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1654,24 +1649,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337690</v>
+        <v>337854</v>
       </c>
       <c r="R10" t="n">
-        <v>6433678</v>
+        <v>6433652</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,7 +1704,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Torrträd med spillkråkehack.</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173153</v>
+        <v>120173335</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,21 +1747,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1772,21 +1771,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338039</v>
+        <v>337690</v>
       </c>
       <c r="R11" t="n">
-        <v>6433662</v>
+        <v>6433678</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,11 +1819,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1971,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173335</v>
+        <v>120173217</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,35 +1978,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2023,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337690</v>
+        <v>337356</v>
       </c>
       <c r="R13" t="n">
-        <v>6433678</v>
+        <v>6433614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2059,6 +2054,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173172</v>
+        <v>120173139</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,31 +2102,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2134,13 +2138,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>337854</v>
+        <v>338044</v>
       </c>
       <c r="R14" t="n">
-        <v>6433652</v>
+        <v>6433666</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2172,17 +2176,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259582</v>
+        <v>120259567</v>
       </c>
       <c r="B16" t="n">
         <v>96198</v>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2366,14 +2366,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338165</v>
+        <v>338072</v>
       </c>
       <c r="R16" t="n">
-        <v>6433704</v>
+        <v>6433703</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259571</v>
+        <v>120259582</v>
       </c>
       <c r="B17" t="n">
-        <v>56292</v>
+        <v>96198</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100088</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2473,31 +2473,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338098</v>
+        <v>338165</v>
       </c>
       <c r="R17" t="n">
-        <v>6433731</v>
+        <v>6433704</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2530,11 +2521,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259579</v>
+        <v>120259558</v>
       </c>
       <c r="B18" t="n">
-        <v>96198</v>
+        <v>91877</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,39 +2560,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2614,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338315</v>
+        <v>338175</v>
       </c>
       <c r="R18" t="n">
-        <v>6433736</v>
+        <v>6433695</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2654,7 +2639,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växte 2 m norr om det ena diket.</t>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,10 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259558</v>
+        <v>120259579</v>
       </c>
       <c r="B19" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,38 +2679,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2733,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338175</v>
+        <v>338315</v>
       </c>
       <c r="R19" t="n">
-        <v>6433695</v>
+        <v>6433736</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2773,7 +2759,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2801,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259567</v>
+        <v>120259576</v>
       </c>
       <c r="B20" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2817,49 +2803,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338072</v>
+        <v>338216</v>
       </c>
       <c r="R20" t="n">
-        <v>6433703</v>
+        <v>6433731</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2891,13 +2869,17 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2916,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259576</v>
+        <v>120259571</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>56292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,16 +2914,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100088</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2949,24 +2931,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338216</v>
+        <v>338098</v>
       </c>
       <c r="R21" t="n">
         <v>6433731</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +2999,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ingick i ett litet meståg.</t>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,6 +3008,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120338581</v>
+        <v>120329487</v>
       </c>
       <c r="B22" t="n">
-        <v>96885</v>
+        <v>94704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3043,24 +3043,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -3071,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338444</v>
+        <v>338473</v>
       </c>
       <c r="R22" t="n">
-        <v>6433736</v>
+        <v>6433748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,11 +3111,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3139,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120338571</v>
+        <v>120338581</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,31 +3150,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3183,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338470</v>
+        <v>338444</v>
       </c>
       <c r="R23" t="n">
-        <v>6433759</v>
+        <v>6433736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3223,7 +3222,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,6 +3231,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120329695</v>
+        <v>120338571</v>
       </c>
       <c r="B25" t="n">
         <v>57336</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338256</v>
+        <v>338470</v>
       </c>
       <c r="R25" t="n">
-        <v>6433688</v>
+        <v>6433759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3451,16 +3451,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3477,10 +3467,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120329487</v>
+        <v>120329695</v>
       </c>
       <c r="B26" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,35 +3479,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3525,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338473</v>
+        <v>338256</v>
       </c>
       <c r="R26" t="n">
-        <v>6433748</v>
+        <v>6433688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3563,15 +3549,29 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120388441</v>
+        <v>120388500</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>96877</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3717,39 +3717,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>224361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3757,10 +3753,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>338129</v>
+        <v>338062</v>
       </c>
       <c r="R28" t="n">
-        <v>6433680</v>
+        <v>6433699</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3797,7 +3793,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 födosökande i tall.</t>
+          <t>Nära vägen, uppe på klippa.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3806,6 +3802,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3824,10 +3821,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120388500</v>
+        <v>120388441</v>
       </c>
       <c r="B29" t="n">
-        <v>96877</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3836,35 +3833,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224361</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3872,10 +3873,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>338062</v>
+        <v>338129</v>
       </c>
       <c r="R29" t="n">
-        <v>6433699</v>
+        <v>6433680</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3912,7 +3913,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Nära vägen, uppe på klippa.</t>
+          <t>1 födosökande i tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,7 +3922,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,6 +3938,121 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120418037</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>337838</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6433643</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växte med tall i hällmarksliknande terräng.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>103441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R2" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B3" t="n">
-        <v>103441</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,9 +829,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R3" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +887,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173153</v>
+        <v>120173172</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,34 +1280,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,13 +1312,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338039</v>
+        <v>337854</v>
       </c>
       <c r="R7" t="n">
-        <v>6433662</v>
+        <v>6433652</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1352,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1361,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1383,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173334</v>
+        <v>120173139</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,42 +1391,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337690</v>
+        <v>338044</v>
       </c>
       <c r="R8" t="n">
-        <v>6433678</v>
+        <v>6433666</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,17 +1469,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Torrträd med spillkråkehack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1494,54 +1494,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120141847</v>
+        <v>120173236</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338147</v>
+        <v>337280</v>
       </c>
       <c r="R9" t="n">
-        <v>6433678</v>
+        <v>6433628</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,17 +1576,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,39 +1599,29 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173172</v>
+        <v>120141847</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1632,45 +1630,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337854</v>
+        <v>338147</v>
       </c>
       <c r="R10" t="n">
-        <v>6433652</v>
+        <v>6433678</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,17 +1688,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,28 +1707,39 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173335</v>
+        <v>120173153</v>
       </c>
       <c r="B11" t="n">
-        <v>96198</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1752,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1771,22 +1776,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>337690</v>
+        <v>338039</v>
       </c>
       <c r="R11" t="n">
-        <v>6433678</v>
+        <v>6433662</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,6 +1823,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173236</v>
+        <v>120173334</v>
       </c>
       <c r="B12" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,39 +1867,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1898,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337280</v>
+        <v>337690</v>
       </c>
       <c r="R12" t="n">
-        <v>6433628</v>
+        <v>6433678</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1938,7 +1939,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,7 +1948,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173217</v>
+        <v>120173335</v>
       </c>
       <c r="B13" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,35 +1978,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337356</v>
+        <v>337690</v>
       </c>
       <c r="R13" t="n">
-        <v>6433614</v>
+        <v>6433678</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2054,11 +2054,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173139</v>
+        <v>120173217</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,35 +2093,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2134,14 +2129,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338044</v>
+        <v>337356</v>
       </c>
       <c r="R14" t="n">
-        <v>6433666</v>
+        <v>6433614</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2174,6 +2169,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2306,19 +2306,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259567</v>
+        <v>120259579</v>
       </c>
       <c r="B16" t="n">
         <v>96198</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2366,14 +2366,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338072</v>
+        <v>338315</v>
       </c>
       <c r="R16" t="n">
-        <v>6433703</v>
+        <v>6433736</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2406,6 +2406,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259582</v>
+        <v>120259571</v>
       </c>
       <c r="B17" t="n">
-        <v>96198</v>
+        <v>56292</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,21 +2454,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100088</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2473,22 +2478,31 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338165</v>
+        <v>338098</v>
       </c>
       <c r="R17" t="n">
-        <v>6433704</v>
+        <v>6433731</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,6 +2535,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,7 +2686,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259579</v>
+        <v>120259567</v>
       </c>
       <c r="B19" t="n">
         <v>96198</v>
@@ -2702,7 +2721,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2715,14 +2734,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338315</v>
+        <v>338072</v>
       </c>
       <c r="R19" t="n">
-        <v>6433736</v>
+        <v>6433703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2755,11 +2774,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,10 +2801,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259576</v>
+        <v>120259582</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,27 +2817,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2831,13 +2853,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338216</v>
+        <v>338165</v>
       </c>
       <c r="R20" t="n">
-        <v>6433731</v>
+        <v>6433704</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2869,17 +2891,13 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ingick i ett litet meståg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2898,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259571</v>
+        <v>120259576</v>
       </c>
       <c r="B21" t="n">
-        <v>56292</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2914,16 +2932,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100088</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2931,41 +2949,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338098</v>
+        <v>338216</v>
       </c>
       <c r="R21" t="n">
         <v>6433731</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2999,7 +3000,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+          <t>Ingick i ett litet meståg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,7 +3009,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120338581</v>
+        <v>120329695</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,31 +3150,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338444</v>
+        <v>338256</v>
       </c>
       <c r="R23" t="n">
-        <v>6433736</v>
+        <v>6433688</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Allmänt spridd i sumdråg i området</t>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,9 +3231,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3356,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120338571</v>
+        <v>120338581</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3368,31 +3377,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3400,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338470</v>
+        <v>338444</v>
       </c>
       <c r="R25" t="n">
-        <v>6433759</v>
+        <v>6433736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3440,7 +3449,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,6 +3458,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3467,7 +3477,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120329695</v>
+        <v>120338571</v>
       </c>
       <c r="B26" t="n">
         <v>57336</v>
@@ -3511,10 +3521,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338256</v>
+        <v>338470</v>
       </c>
       <c r="R26" t="n">
-        <v>6433688</v>
+        <v>6433759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3561,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,16 +3572,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3588,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120391007</v>
+        <v>120388441</v>
       </c>
       <c r="B27" t="n">
-        <v>94344</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3600,45 +3600,53 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skår 1, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337877</v>
+        <v>338129</v>
       </c>
       <c r="R27" t="n">
-        <v>6433714</v>
+        <v>6433680</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3665,19 +3673,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 födosökande i tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,19 +3689,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3821,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120388441</v>
+        <v>120391007</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>94344</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3833,53 +3835,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Risveden/Sopekärr, Vg</t>
+          <t>Skår 1, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>338129</v>
+        <v>337877</v>
       </c>
       <c r="R29" t="n">
-        <v>6433680</v>
+        <v>6433714</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3906,14 +3900,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 födosökande i tall.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,18 +3921,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -1494,62 +1494,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173236</v>
+        <v>120141847</v>
       </c>
       <c r="B9" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337280</v>
+        <v>338147</v>
       </c>
       <c r="R9" t="n">
-        <v>6433628</v>
+        <v>6433678</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,17 +1568,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,69 +1591,87 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120141847</v>
+        <v>120173236</v>
       </c>
       <c r="B10" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338147</v>
+        <v>337280</v>
       </c>
       <c r="R10" t="n">
-        <v>6433678</v>
+        <v>6433628</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1688,17 +1698,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,25 +1721,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>91877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,31 +1039,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R5" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141319</v>
+        <v>120141657</v>
       </c>
       <c r="B6" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338174</v>
+        <v>338153</v>
       </c>
       <c r="R6" t="n">
-        <v>6433694</v>
+        <v>6433685</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173172</v>
+        <v>120173334</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,20 +1276,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1297,28 +1297,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337854</v>
+        <v>337690</v>
       </c>
       <c r="R7" t="n">
-        <v>6433652</v>
+        <v>6433678</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173139</v>
+        <v>120173153</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,35 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1431,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338044</v>
+        <v>338039</v>
       </c>
       <c r="R8" t="n">
-        <v>6433666</v>
+        <v>6433662</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,6 +1462,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,14 +1494,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120141847</v>
+        <v>120173172</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1510,41 +1510,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338147</v>
+        <v>337854</v>
       </c>
       <c r="R9" t="n">
-        <v>6433678</v>
+        <v>6433652</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,29 +1591,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1736,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173153</v>
+        <v>120173139</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,34 +1745,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1787,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338039</v>
+        <v>338044</v>
       </c>
       <c r="R11" t="n">
-        <v>6433662</v>
+        <v>6433666</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1823,11 +1817,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173334</v>
+        <v>120173335</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,31 +1856,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1937,17 +1934,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Torrträd med spillkråkehack.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173335</v>
+        <v>120173217</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,35 +1971,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2018,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337690</v>
+        <v>337356</v>
       </c>
       <c r="R13" t="n">
-        <v>6433678</v>
+        <v>6433614</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2054,6 +2047,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,62 +2079,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173217</v>
+        <v>120141847</v>
       </c>
       <c r="B14" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>337356</v>
+        <v>338147</v>
       </c>
       <c r="R14" t="n">
-        <v>6433614</v>
+        <v>6433678</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2163,17 +2153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,15 +2176,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259571</v>
+        <v>120259567</v>
       </c>
       <c r="B17" t="n">
-        <v>56292</v>
+        <v>96198</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,55 +2454,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100088</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338098</v>
+        <v>338072</v>
       </c>
       <c r="R17" t="n">
-        <v>6433731</v>
+        <v>6433703</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2535,11 +2526,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2553,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259558</v>
+        <v>120259576</v>
       </c>
       <c r="B18" t="n">
-        <v>91877</v>
+        <v>57689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2579,38 +2565,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1440</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2618,13 +2597,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338175</v>
+        <v>338216</v>
       </c>
       <c r="R18" t="n">
-        <v>6433695</v>
+        <v>6433731</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2658,7 +2637,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
+          <t>Ingick i ett litet meståg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,7 +2646,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259567</v>
+        <v>120259582</v>
       </c>
       <c r="B19" t="n">
         <v>96198</v>
@@ -2721,12 +2699,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2734,14 +2712,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338072</v>
+        <v>338165</v>
       </c>
       <c r="R19" t="n">
-        <v>6433703</v>
+        <v>6433704</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2801,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259582</v>
+        <v>120259571</v>
       </c>
       <c r="B20" t="n">
-        <v>96198</v>
+        <v>56292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2817,21 +2795,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100088</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2841,22 +2819,31 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338165</v>
+        <v>338098</v>
       </c>
       <c r="R20" t="n">
-        <v>6433704</v>
+        <v>6433731</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2889,6 +2876,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2908,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259576</v>
+        <v>120259558</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>91877</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,31 +2920,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>1440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2960,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338216</v>
+        <v>338175</v>
       </c>
       <c r="R21" t="n">
-        <v>6433731</v>
+        <v>6433695</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +2999,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ingick i ett litet meståg.</t>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,6 +3008,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120329487</v>
+        <v>120329695</v>
       </c>
       <c r="B22" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,35 +3039,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3075,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338473</v>
+        <v>338256</v>
       </c>
       <c r="R22" t="n">
-        <v>6433748</v>
+        <v>6433688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3113,15 +3109,29 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3138,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120329695</v>
+        <v>120338581</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,31 +3160,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3182,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338256</v>
+        <v>338444</v>
       </c>
       <c r="R23" t="n">
-        <v>6433688</v>
+        <v>6433736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3232,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,18 +3241,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3365,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120338581</v>
+        <v>120329487</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>94704</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3381,24 +3382,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -3409,10 +3414,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338444</v>
+        <v>338473</v>
       </c>
       <c r="R25" t="n">
-        <v>6433736</v>
+        <v>6433748</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3445,11 +3450,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4053,6 +4053,252 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120388967</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>338002</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6433653</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växandes på bergsåsen ihop med tall I äldre tidigare skogsbetad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120388836</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96877</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>337976</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6433682</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 st knippen växandes på bergsåsen.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre skogsbetad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B2" t="n">
-        <v>103441</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R2" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>103441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,13 +832,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R3" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141319</v>
+        <v>120141657</v>
       </c>
       <c r="B5" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1039,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338174</v>
+        <v>338153</v>
       </c>
       <c r="R5" t="n">
-        <v>6433694</v>
+        <v>6433685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,17 +1101,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,17 +1137,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B6" t="n">
-        <v>96198</v>
+        <v>91877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,31 +1156,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R6" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173334</v>
+        <v>120173217</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,31 +1276,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337690</v>
+        <v>337356</v>
       </c>
       <c r="R7" t="n">
-        <v>6433678</v>
+        <v>6433614</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,7 +1356,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Torrträd med spillkråkehack.</t>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,6 +1365,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173153</v>
+        <v>120173334</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,49 +1396,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338039</v>
+        <v>337690</v>
       </c>
       <c r="R8" t="n">
-        <v>6433662</v>
+        <v>6433678</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,7 +1468,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1477,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1494,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173172</v>
+        <v>120173153</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,31 +1511,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1542,13 +1546,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337854</v>
+        <v>338039</v>
       </c>
       <c r="R9" t="n">
-        <v>6433652</v>
+        <v>6433662</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1586,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,6 +1595,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1729,14 +1734,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173139</v>
+        <v>120141847</v>
       </c>
       <c r="B11" t="n">
         <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1762,29 +1767,21 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338044</v>
+        <v>338147</v>
       </c>
       <c r="R11" t="n">
-        <v>6433666</v>
+        <v>6433678</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,12 +1808,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,25 +1831,35 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173335</v>
+        <v>120173172</v>
       </c>
       <c r="B12" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,49 +1872,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337690</v>
+        <v>337854</v>
       </c>
       <c r="R12" t="n">
-        <v>6433678</v>
+        <v>6433652</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1934,13 +1942,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173217</v>
+        <v>120173139</v>
       </c>
       <c r="B13" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,35 +1983,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2007,14 +2019,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337356</v>
+        <v>338044</v>
       </c>
       <c r="R13" t="n">
-        <v>6433614</v>
+        <v>6433666</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2047,11 +2059,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,14 +2086,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120141847</v>
+        <v>120173335</v>
       </c>
       <c r="B14" t="n">
         <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2112,18 +2119,26 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338147</v>
+        <v>337690</v>
       </c>
       <c r="R14" t="n">
         <v>6433678</v>
@@ -2153,17 +2168,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,25 +2186,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259579</v>
+        <v>120259571</v>
       </c>
       <c r="B16" t="n">
-        <v>96198</v>
+        <v>56292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,46 +2334,55 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>100088</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338315</v>
+        <v>338098</v>
       </c>
       <c r="R16" t="n">
-        <v>6433736</v>
+        <v>6433731</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2410,7 +2419,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växte 2 m norr om det ena diket.</t>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259567</v>
+        <v>120259576</v>
       </c>
       <c r="B17" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,49 +2463,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338072</v>
+        <v>338216</v>
       </c>
       <c r="R17" t="n">
-        <v>6433703</v>
+        <v>6433731</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2528,13 +2529,17 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2553,10 +2558,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259576</v>
+        <v>120259579</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,27 +2574,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2597,13 +2610,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338216</v>
+        <v>338315</v>
       </c>
       <c r="R18" t="n">
-        <v>6433731</v>
+        <v>6433736</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2637,7 +2650,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ingick i ett litet meståg.</t>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,6 +2659,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2664,7 +2678,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259582</v>
+        <v>120259567</v>
       </c>
       <c r="B19" t="n">
         <v>96198</v>
@@ -2699,12 +2713,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2712,14 +2726,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338165</v>
+        <v>338072</v>
       </c>
       <c r="R19" t="n">
-        <v>6433704</v>
+        <v>6433703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2779,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259571</v>
+        <v>120259558</v>
       </c>
       <c r="B20" t="n">
-        <v>56292</v>
+        <v>91877</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,59 +2805,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100088</v>
+        <v>1440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338098</v>
+        <v>338175</v>
       </c>
       <c r="R20" t="n">
-        <v>6433731</v>
+        <v>6433695</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2880,7 +2884,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2908,10 +2912,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259558</v>
+        <v>120259582</v>
       </c>
       <c r="B21" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2920,38 +2924,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338175</v>
+        <v>338165</v>
       </c>
       <c r="R21" t="n">
-        <v>6433695</v>
+        <v>6433704</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2995,11 +3000,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120338581</v>
+        <v>120329487</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>94704</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3164,24 +3164,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -3192,10 +3196,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338444</v>
+        <v>338473</v>
       </c>
       <c r="R23" t="n">
-        <v>6433736</v>
+        <v>6433748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3228,11 +3232,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3366,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120329487</v>
+        <v>120338571</v>
       </c>
       <c r="B25" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3378,35 +3377,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3414,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338473</v>
+        <v>338470</v>
       </c>
       <c r="R25" t="n">
-        <v>6433748</v>
+        <v>6433759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3452,13 +3447,17 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3477,10 +3476,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120338571</v>
+        <v>120338581</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,31 +3488,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338470</v>
+        <v>338444</v>
       </c>
       <c r="R26" t="n">
-        <v>6433759</v>
+        <v>6433736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3561,7 +3560,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3570,6 +3569,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120388441</v>
+        <v>120388500</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>96877</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3600,39 +3600,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>224361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3640,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>338129</v>
+        <v>338062</v>
       </c>
       <c r="R27" t="n">
-        <v>6433680</v>
+        <v>6433699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3680,7 +3676,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1 födosökande i tall.</t>
+          <t>Nära vägen, uppe på klippa.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,6 +3685,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120388500</v>
+        <v>120391007</v>
       </c>
       <c r="B28" t="n">
-        <v>96877</v>
+        <v>94344</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,45 +3720,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>224361</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Risveden/Sopekärr, Vg</t>
+          <t>Skår 1, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>338062</v>
+        <v>337877</v>
       </c>
       <c r="R28" t="n">
-        <v>6433699</v>
+        <v>6433714</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3788,14 +3781,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Nära vägen, uppe på klippa.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,22 +3809,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120391007</v>
+        <v>120388441</v>
       </c>
       <c r="B29" t="n">
-        <v>94344</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,45 +3833,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skår 1, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>337877</v>
+        <v>338129</v>
       </c>
       <c r="R29" t="n">
-        <v>6433714</v>
+        <v>6433680</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3900,19 +3906,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 födosökande i tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,19 +3922,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4299,6 +4299,127 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120508110</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skår 1, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>337877</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6433714</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120329487</v>
+        <v>120329674</v>
       </c>
       <c r="B23" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3164,31 +3164,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3196,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338473</v>
+        <v>338302</v>
       </c>
       <c r="R23" t="n">
-        <v>6433748</v>
+        <v>6433745</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3240,7 +3236,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120329674</v>
+        <v>120329487</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>94704</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3275,27 +3270,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3303,10 +3302,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338302</v>
+        <v>338473</v>
       </c>
       <c r="R24" t="n">
-        <v>6433745</v>
+        <v>6433748</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3347,6 +3346,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +4420,1103 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120403484</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skårs lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>337529</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6433624</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>på trädstam</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120402038</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96654</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2617</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Flikbålmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Riccardia multifida</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med honorgan</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skårs lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>337592</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6433638</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120403721</v>
+      </c>
+      <c r="B36" t="n">
+        <v>94227</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>338122</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6433725</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120402158</v>
+      </c>
+      <c r="B37" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skårs lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>337348</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6433649</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120403713</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>338122</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6433725</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på aspstammar och på sten i branten</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120403115</v>
+      </c>
+      <c r="B39" t="n">
+        <v>94346</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skars lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>337504</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6433647</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120402288</v>
+      </c>
+      <c r="B40" t="n">
+        <v>94433</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skårs lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>337348</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6433653</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>på trädstammar och på sten i branten</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120403294</v>
+      </c>
+      <c r="B41" t="n">
+        <v>94437</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skars lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>337431</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6433595</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>täckte stambaser på asp</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120402999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>103441</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skårs lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>337376</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6433642</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,62 +1264,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173217</v>
+        <v>120141847</v>
       </c>
       <c r="B7" t="n">
-        <v>105588</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337356</v>
+        <v>338147</v>
       </c>
       <c r="R7" t="n">
-        <v>6433614</v>
+        <v>6433678</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,17 +1338,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,25 +1361,35 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173334</v>
+        <v>120173139</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,42 +1398,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337690</v>
+        <v>338044</v>
       </c>
       <c r="R8" t="n">
-        <v>6433678</v>
+        <v>6433666</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1466,17 +1476,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Torrträd med spillkråkehack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1495,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173153</v>
+        <v>120173172</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>57689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,34 +1517,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1546,13 +1549,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338039</v>
+        <v>337854</v>
       </c>
       <c r="R9" t="n">
-        <v>6433662</v>
+        <v>6433652</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,7 +1589,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,7 +1598,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1614,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173236</v>
+        <v>120173153</v>
       </c>
       <c r="B10" t="n">
-        <v>105588</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,50 +1628,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337280</v>
+        <v>338039</v>
       </c>
       <c r="R10" t="n">
-        <v>6433628</v>
+        <v>6433662</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1706,7 +1707,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,14 +1735,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120141847</v>
+        <v>120173335</v>
       </c>
       <c r="B11" t="n">
         <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1767,18 +1768,26 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338147</v>
+        <v>337690</v>
       </c>
       <c r="R11" t="n">
         <v>6433678</v>
@@ -1808,17 +1817,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,35 +1835,25 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173172</v>
+        <v>120173236</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>105588</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,49 +1862,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337854</v>
+        <v>337280</v>
       </c>
       <c r="R12" t="n">
-        <v>6433652</v>
+        <v>6433628</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1944,7 +1942,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,6 +1951,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1971,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173139</v>
+        <v>120173334</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,50 +1982,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338044</v>
+        <v>337690</v>
       </c>
       <c r="R13" t="n">
-        <v>6433666</v>
+        <v>6433678</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2061,13 +2052,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Torrträd med spillkråkehack.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173335</v>
+        <v>120173217</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,35 +2093,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2138,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>337690</v>
+        <v>337356</v>
       </c>
       <c r="R14" t="n">
-        <v>6433678</v>
+        <v>6433614</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2174,6 +2169,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259571</v>
+        <v>120259579</v>
       </c>
       <c r="B16" t="n">
-        <v>56292</v>
+        <v>96198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,55 +2334,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100088</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Intakan. öster om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338098</v>
+        <v>338315</v>
       </c>
       <c r="R16" t="n">
-        <v>6433731</v>
+        <v>6433736</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2419,7 +2410,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259576</v>
+        <v>120259567</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,41 +2454,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338216</v>
+        <v>338072</v>
       </c>
       <c r="R17" t="n">
-        <v>6433731</v>
+        <v>6433703</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2529,17 +2528,13 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ingick i ett litet meståg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2553,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259579</v>
+        <v>120259582</v>
       </c>
       <c r="B18" t="n">
         <v>96198</v>
@@ -2593,12 +2588,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2610,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338315</v>
+        <v>338165</v>
       </c>
       <c r="R18" t="n">
-        <v>6433736</v>
+        <v>6433704</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2646,11 +2641,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259567</v>
+        <v>120259571</v>
       </c>
       <c r="B19" t="n">
-        <v>96198</v>
+        <v>56292</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2694,46 +2684,55 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100088</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan. öster om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338072</v>
+        <v>338098</v>
       </c>
       <c r="R19" t="n">
-        <v>6433703</v>
+        <v>6433731</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2766,6 +2765,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259582</v>
+        <v>120259576</v>
       </c>
       <c r="B21" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,35 +2932,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2964,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338165</v>
+        <v>338216</v>
       </c>
       <c r="R21" t="n">
-        <v>6433704</v>
+        <v>6433731</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3002,13 +2998,17 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120329695</v>
+        <v>120329487</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,31 +3039,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3071,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338256</v>
+        <v>338473</v>
       </c>
       <c r="R22" t="n">
-        <v>6433688</v>
+        <v>6433748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,29 +3113,15 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3148,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120329674</v>
+        <v>120329695</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,20 +3150,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3192,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338302</v>
+        <v>338256</v>
       </c>
       <c r="R23" t="n">
-        <v>6433745</v>
+        <v>6433688</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,6 +3220,11 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3238,6 +3233,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3254,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120329487</v>
+        <v>120329674</v>
       </c>
       <c r="B24" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3270,31 +3275,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3302,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338473</v>
+        <v>338302</v>
       </c>
       <c r="R24" t="n">
-        <v>6433748</v>
+        <v>6433745</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3347,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120338571</v>
+        <v>120338581</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,31 +3377,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338470</v>
+        <v>338444</v>
       </c>
       <c r="R25" t="n">
-        <v>6433759</v>
+        <v>6433736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,6 +3458,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3477,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120338581</v>
+        <v>120338571</v>
       </c>
       <c r="B26" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,31 +3489,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338444</v>
+        <v>338470</v>
       </c>
       <c r="R26" t="n">
-        <v>6433736</v>
+        <v>6433759</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3560,7 +3561,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Allmänt spridd i sumdråg i området</t>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,7 +3570,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120388967</v>
+        <v>120388836</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>96877</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4067,34 +4067,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4102,10 +4103,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>338002</v>
+        <v>337976</v>
       </c>
       <c r="R31" t="n">
-        <v>6433653</v>
+        <v>6433682</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4142,7 +4143,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växandes på bergsåsen ihop med tall I äldre tidigare skogsbetad barrblandskog.</t>
+          <t>4 st knippen växandes på bergsåsen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4158,6 +4159,11 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4175,10 +4181,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120388836</v>
+        <v>120388967</v>
       </c>
       <c r="B32" t="n">
-        <v>96877</v>
+        <v>91881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4187,35 +4193,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224361</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4223,10 +4228,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>337976</v>
+        <v>338002</v>
       </c>
       <c r="R32" t="n">
-        <v>6433682</v>
+        <v>6433653</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4263,7 +4268,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 st knippen växandes på bergsåsen.</t>
+          <t>Växandes på bergsåsen ihop med tall I äldre tidigare skogsbetad barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4279,11 +4284,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120402038</v>
+        <v>120402999</v>
       </c>
       <c r="B35" t="n">
-        <v>96654</v>
+        <v>103441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,25 +4574,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2617</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4600,16 +4600,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med honorgan</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4618,10 +4610,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>337592</v>
+        <v>337376</v>
       </c>
       <c r="R35" t="n">
-        <v>6433638</v>
+        <v>6433642</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4654,11 +4646,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5039,14 +5026,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403115</v>
+        <v>120402288</v>
       </c>
       <c r="B39" t="n">
-        <v>94346</v>
+        <v>94433</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5055,21 +5042,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2813</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5083,14 +5070,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skars lid, Vg</t>
+          <t>Skårs lid, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>337504</v>
+        <v>337348</v>
       </c>
       <c r="R39" t="n">
-        <v>6433647</v>
+        <v>6433653</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5125,6 +5112,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>på trädstammar och på sten i branten</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5134,6 +5126,21 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5150,10 +5157,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120402288</v>
+        <v>120388678</v>
       </c>
       <c r="B40" t="n">
-        <v>94433</v>
+        <v>91881</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5162,46 +5169,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skårs lid, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>337348</v>
+        <v>337981</v>
       </c>
       <c r="R40" t="n">
-        <v>6433653</v>
+        <v>6433658</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5238,7 +5244,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>på trädstammar och på sten i branten</t>
+          <t>Växer på bergsåsen intill tallar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5251,44 +5257,39 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bergsås i äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Grimhild Angertuva, Liv Vikingson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403294</v>
+        <v>120403115</v>
       </c>
       <c r="B41" t="n">
-        <v>94437</v>
+        <v>94346</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5297,24 +5298,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2668</v>
+        <v>2813</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -5325,13 +5330,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>337431</v>
+        <v>337504</v>
       </c>
       <c r="R41" t="n">
-        <v>6433595</v>
+        <v>6433647</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5361,11 +5366,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>täckte stambaser på asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5377,21 +5377,6 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5408,37 +5393,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120402999</v>
+        <v>120402038</v>
       </c>
       <c r="B42" t="n">
-        <v>103441</v>
+        <v>96654</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222412</v>
+        <v>2617</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5446,8 +5431,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med honorgan</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5456,10 +5449,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>337376</v>
+        <v>337592</v>
       </c>
       <c r="R42" t="n">
-        <v>6433642</v>
+        <v>6433638</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5494,6 +5487,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5516,6 +5514,133 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120403294</v>
+      </c>
+      <c r="B43" t="n">
+        <v>94437</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skars lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>337431</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6433595</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>täckte stambaser på asp</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119979670</v>
+        <v>119973533</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>103441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337381</v>
+        <v>337435</v>
       </c>
       <c r="R2" t="n">
-        <v>6433648</v>
+        <v>6433669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119973533</v>
+        <v>119979670</v>
       </c>
       <c r="B3" t="n">
-        <v>103441</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,9 +829,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337435</v>
+        <v>337381</v>
       </c>
       <c r="R3" t="n">
-        <v>6433669</v>
+        <v>6433648</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +887,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120141657</v>
+        <v>120141319</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>91877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,31 +1039,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338153</v>
+        <v>338174</v>
       </c>
       <c r="R5" t="n">
-        <v>6433685</v>
+        <v>6433694</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>I blandbarrskog på stig intill ett kärr.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Grimhild Angertuva, Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120141319</v>
+        <v>120141657</v>
       </c>
       <c r="B6" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338174</v>
+        <v>338153</v>
       </c>
       <c r="R6" t="n">
-        <v>6433694</v>
+        <v>6433685</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I blandbarrskog på stig intill ett kärr.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,61 +1257,69 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120141847</v>
+        <v>120173236</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>105588</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ale Skår 2:8, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338147</v>
+        <v>337280</v>
       </c>
       <c r="R7" t="n">
-        <v>6433678</v>
+        <v>6433628</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,17 +1346,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med stor revmossa</t>
+          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,35 +1369,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre tidigare skogsbetad blandskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173139</v>
+        <v>120173153</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,35 +1400,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1438,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338044</v>
+        <v>338039</v>
       </c>
       <c r="R8" t="n">
-        <v>6433666</v>
+        <v>6433662</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,6 +1471,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173172</v>
+        <v>120173217</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>105588</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,49 +1515,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337854</v>
+        <v>337356</v>
       </c>
       <c r="R9" t="n">
-        <v>6433652</v>
+        <v>6433614</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,7 +1595,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
+          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1616,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173153</v>
+        <v>120173335</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>96198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,21 +1639,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1656,21 +1663,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intakan, söder om, Vg</t>
+          <t>Intakan, sydväst om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338039</v>
+        <v>337690</v>
       </c>
       <c r="R10" t="n">
-        <v>6433662</v>
+        <v>6433678</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1703,11 +1711,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar, 6 och 7 cm breda växte utmed en liten stig på en berghöjd med hällmarkstallskog.  2 m från en medelgrov tall och 1 m från en ung gran. Bland ljung, lingon och mossa.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,7 +1738,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120173335</v>
+        <v>120173139</v>
       </c>
       <c r="B11" t="n">
         <v>96198</v>
@@ -1770,12 +1773,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1783,14 +1786,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>337690</v>
+        <v>338044</v>
       </c>
       <c r="R11" t="n">
-        <v>6433678</v>
+        <v>6433666</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1850,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120173236</v>
+        <v>120173334</v>
       </c>
       <c r="B12" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,39 +1865,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337280</v>
+        <v>337690</v>
       </c>
       <c r="R12" t="n">
-        <v>6433628</v>
+        <v>6433678</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Strax öster om huset norr om landsvägen stod en grov ask med en omkrets på 220 cm i brösthöjd. Trädet var skadat och halvdött, troligen p g a askskottssjukan.</t>
+          <t>Torrträd med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,7 +1946,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1970,51 +1964,51 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173334</v>
+        <v>120141847</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Ale Skår 2:8, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337690</v>
+        <v>338147</v>
       </c>
       <c r="R13" t="n">
         <v>6433678</v>
@@ -2044,17 +2038,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Torrträd med spillkråkehack.</t>
+          <t>Rikligt med stor revmossa</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,28 +2057,39 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre tidigare skogsbetad blandskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173217</v>
+        <v>120173172</v>
       </c>
       <c r="B14" t="n">
-        <v>105588</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,53 +2098,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Intakan, sydväst om, Vg</t>
+          <t>Intakan, söder om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>337356</v>
+        <v>337854</v>
       </c>
       <c r="R14" t="n">
-        <v>6433614</v>
+        <v>6433652</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2173,7 +2174,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5-6 medelgrova askar som var döda eller skadade, troligen p g a askskottssjukan. Ytterligare en handfull träd stod lite längre nedströms, i kanten på skogen.</t>
+          <t>Ett litet meståg med bl a en handfull kungsfåglar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,7 +2183,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259579</v>
+        <v>120259558</v>
       </c>
       <c r="B16" t="n">
-        <v>96198</v>
+        <v>91877</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,39 +2330,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>1440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2370,10 +2369,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338315</v>
+        <v>338175</v>
       </c>
       <c r="R16" t="n">
-        <v>6433736</v>
+        <v>6433695</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2410,7 +2409,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växte 2 m norr om det ena diket.</t>
+          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259567</v>
+        <v>120259576</v>
       </c>
       <c r="B17" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,49 +2453,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Intakan, sydost om, Vg</t>
+          <t>Intakan, öster om, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338072</v>
+        <v>338216</v>
       </c>
       <c r="R17" t="n">
-        <v>6433703</v>
+        <v>6433731</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2528,13 +2519,17 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2553,7 +2548,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259582</v>
+        <v>120259567</v>
       </c>
       <c r="B18" t="n">
         <v>96198</v>
@@ -2588,12 +2583,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2601,14 +2596,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Intakan, öster om, Vg</t>
+          <t>Intakan, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338165</v>
+        <v>338072</v>
       </c>
       <c r="R18" t="n">
-        <v>6433704</v>
+        <v>6433703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2797,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259558</v>
+        <v>120259582</v>
       </c>
       <c r="B20" t="n">
-        <v>91877</v>
+        <v>96198</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,38 +2804,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1440</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2848,10 +2844,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338175</v>
+        <v>338165</v>
       </c>
       <c r="R20" t="n">
-        <v>6433695</v>
+        <v>6433704</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2884,11 +2880,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar, övergångna eller mycket övergångna, växte direkt söder om det södra diket som avgränsar en öppen miljö i skogen, invid en stig. Två av de minst övergångna fruktkropparna togs hem som kollekt. Växte med husmossa, blåbär och sphagnum 2 m från en sälg, 2 m från en knappt medelgrov gran och 7 m från en medelgrov glasbjörk. Flera av fruktkropparna var ganska stora. Den största medtagna fruktkroppen hade en 23 cm bred hatt som var blöt men där den var som bäst välbehållen hade en beageaktig färg, lite mot blekgul. Övriga delar av hatten brunare. Hattöversidan slät men med tecken på skinntunna, platta fjäll i den centrala delen. I övrigt radiärt trådig. Viss brun zonering. Bruna nedlöpande taggar, 10-12 mm, en del med ljusare spetsar. Foten 8,5 cm lång och 2,5 cm bred, brun i den övre hälften och allt vitare ner mot basen. Köttet blekt gulbeige men med lite mörkare partier, troligen där den var blötare. Lukt tydligt väldoftande, sötaktig, som parfym, ev curryton. Smaken mild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2907,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259576</v>
+        <v>120259579</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,27 +2923,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2960,13 +2959,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338216</v>
+        <v>338315</v>
       </c>
       <c r="R21" t="n">
-        <v>6433731</v>
+        <v>6433736</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +2999,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ingick i ett litet meståg.</t>
+          <t>Växte 2 m norr om det ena diket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,6 +3008,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120329487</v>
+        <v>120329674</v>
       </c>
       <c r="B22" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3043,31 +3043,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3075,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338473</v>
+        <v>338302</v>
       </c>
       <c r="R22" t="n">
-        <v>6433748</v>
+        <v>6433745</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3119,7 +3115,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3138,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120329695</v>
+        <v>120338581</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,31 +3145,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3182,10 +3177,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338256</v>
+        <v>338444</v>
       </c>
       <c r="R23" t="n">
-        <v>6433688</v>
+        <v>6433736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3217,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tall.</t>
+          <t>Allmänt spridd i sumdråg i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,18 +3226,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3259,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120329674</v>
+        <v>120329487</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>94704</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3275,27 +3261,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3303,10 +3293,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338302</v>
+        <v>338473</v>
       </c>
       <c r="R24" t="n">
-        <v>6433745</v>
+        <v>6433748</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3347,6 +3337,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3365,10 +3356,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120338581</v>
+        <v>120329695</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,31 +3368,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3409,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338444</v>
+        <v>338256</v>
       </c>
       <c r="R25" t="n">
-        <v>6433736</v>
+        <v>6433688</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3449,7 +3440,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Allmänt spridd i sumdråg i området</t>
+          <t>Färskt spår av födosökande spillkråka på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,9 +3449,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Flerskiktad blandskog med inslag av sumpdråg</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120391007</v>
+        <v>120388441</v>
       </c>
       <c r="B28" t="n">
-        <v>94344</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,45 +3716,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skår 1, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>337877</v>
+        <v>338129</v>
       </c>
       <c r="R28" t="n">
-        <v>6433714</v>
+        <v>6433680</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3781,19 +3789,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 födosökande i tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3802,29 +3805,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120388441</v>
+        <v>120391007</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>94344</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3833,53 +3835,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Risveden/Sopekärr, Vg</t>
+          <t>Skår 1, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>338129</v>
+        <v>337877</v>
       </c>
       <c r="R29" t="n">
-        <v>6433680</v>
+        <v>6433714</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3906,14 +3900,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 födosökande i tall.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,18 +3921,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120388836</v>
+        <v>120388967</v>
       </c>
       <c r="B31" t="n">
-        <v>96877</v>
+        <v>91881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4067,35 +4067,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224361</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4103,10 +4102,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>337976</v>
+        <v>338002</v>
       </c>
       <c r="R31" t="n">
-        <v>6433682</v>
+        <v>6433653</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4143,7 +4142,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>4 st knippen växandes på bergsåsen.</t>
+          <t>Växandes på bergsåsen ihop med tall I äldre tidigare skogsbetad barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4159,11 +4158,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4181,10 +4175,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120388967</v>
+        <v>120388836</v>
       </c>
       <c r="B32" t="n">
-        <v>91881</v>
+        <v>96877</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4193,34 +4187,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>224361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4228,10 +4223,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>338002</v>
+        <v>337976</v>
       </c>
       <c r="R32" t="n">
-        <v>6433653</v>
+        <v>6433682</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4268,7 +4263,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växandes på bergsåsen ihop med tall I äldre tidigare skogsbetad barrblandskog.</t>
+          <t>4 st knippen växandes på bergsåsen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,6 +4279,11 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120403484</v>
+        <v>120403713</v>
       </c>
       <c r="B34" t="n">
-        <v>96198</v>
+        <v>94433</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4438,31 +4438,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2569</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4470,17 +4470,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skårs lid, Vg</t>
+          <t>Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>337529</v>
+        <v>338122</v>
       </c>
       <c r="R34" t="n">
-        <v>6433624</v>
+        <v>6433725</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på trädstam</t>
+          <t>på aspstammar och på sten i branten</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4526,26 +4526,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Betula pendula</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4562,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120402999</v>
+        <v>120403721</v>
       </c>
       <c r="B35" t="n">
-        <v>103441</v>
+        <v>94227</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,45 +4558,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>2779</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skårs lid, Vg</t>
+          <t>Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>337376</v>
+        <v>338122</v>
       </c>
       <c r="R35" t="n">
-        <v>6433642</v>
+        <v>6433725</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4673,10 +4649,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403721</v>
+        <v>120402158</v>
       </c>
       <c r="B36" t="n">
-        <v>94227</v>
+        <v>94433</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4689,41 +4665,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Vg</t>
+          <t>Skårs lid, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>338122</v>
+        <v>337348</v>
       </c>
       <c r="R36" t="n">
-        <v>6433725</v>
+        <v>6433649</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4764,6 +4744,21 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4780,10 +4775,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120402158</v>
+        <v>120403484</v>
       </c>
       <c r="B37" t="n">
-        <v>94433</v>
+        <v>96198</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4796,29 +4791,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2667</v>
+        <v>2569</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4828,10 +4827,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>337348</v>
+        <v>337529</v>
       </c>
       <c r="R37" t="n">
-        <v>6433649</v>
+        <v>6433624</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4866,6 +4865,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på trädstam</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4878,17 +4882,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Stem on living tree # Betula pendula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4906,10 +4915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403713</v>
+        <v>120402999</v>
       </c>
       <c r="B38" t="n">
-        <v>94433</v>
+        <v>103441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4922,49 +4931,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2667</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Vg</t>
+          <t>Skårs lid, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>338122</v>
+        <v>337376</v>
       </c>
       <c r="R38" t="n">
-        <v>6433725</v>
+        <v>6433642</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4994,11 +4999,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på aspstammar och på sten i branten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5026,58 +5026,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120402288</v>
+        <v>120388678</v>
       </c>
       <c r="B39" t="n">
-        <v>94433</v>
+        <v>91881</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skårs lid, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>337348</v>
+        <v>337981</v>
       </c>
       <c r="R39" t="n">
-        <v>6433653</v>
+        <v>6433658</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5114,7 +5113,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på trädstammar och på sten i branten</t>
+          <t>Växer på bergsåsen intill tallar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5127,87 +5126,83 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Bergsås i äldre skogsbetad barrblandskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Grimhild Angertuva, Liv Vikingson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120388678</v>
+        <v>120403115</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>94346</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2813</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mickelsdamm Skår, Vg</t>
+          <t>Skars lid, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>337981</v>
+        <v>337504</v>
       </c>
       <c r="R40" t="n">
-        <v>6433658</v>
+        <v>6433647</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5242,11 +5237,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer på bergsåsen intill tallar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5257,35 +5247,25 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Bergsås i äldre skogsbetad barrblandskog</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva, Liv Vikingson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403115</v>
+        <v>120402288</v>
       </c>
       <c r="B41" t="n">
-        <v>94346</v>
+        <v>94433</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5298,21 +5278,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2813</v>
+        <v>2667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5326,14 +5306,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skars lid, Vg</t>
+          <t>Skårs lid, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>337504</v>
+        <v>337348</v>
       </c>
       <c r="R41" t="n">
-        <v>6433647</v>
+        <v>6433653</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5368,6 +5348,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>på trädstammar och på sten i branten</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5377,6 +5362,21 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6270,7 +6270,7 @@
         <v>121349455</v>
       </c>
       <c r="B49" t="n">
-        <v>97019</v>
+        <v>97029</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>121349471</v>
       </c>
       <c r="B50" t="n">
-        <v>97019</v>
+        <v>97029</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6270,7 +6270,7 @@
         <v>121349455</v>
       </c>
       <c r="B49" t="n">
-        <v>97029</v>
+        <v>97042</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>121349471</v>
       </c>
       <c r="B50" t="n">
-        <v>97029</v>
+        <v>97042</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6267,10 +6267,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349455</v>
+        <v>121349471</v>
       </c>
       <c r="B49" t="n">
-        <v>97042</v>
+        <v>97043</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337917</v>
+        <v>337968</v>
       </c>
       <c r="R49" t="n">
-        <v>6433695</v>
+        <v>6433680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,10 +6379,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121349471</v>
+        <v>121349455</v>
       </c>
       <c r="B50" t="n">
-        <v>97042</v>
+        <v>97043</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>337968</v>
+        <v>337917</v>
       </c>
       <c r="R50" t="n">
-        <v>6433680</v>
+        <v>6433695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6270,7 +6270,7 @@
         <v>121349471</v>
       </c>
       <c r="B49" t="n">
-        <v>97043</v>
+        <v>97046</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>121349455</v>
       </c>
       <c r="B50" t="n">
-        <v>97043</v>
+        <v>97046</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6267,7 +6267,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349471</v>
+        <v>121349455</v>
       </c>
       <c r="B49" t="n">
         <v>97046</v>
@@ -6298,7 +6298,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337968</v>
+        <v>337917</v>
       </c>
       <c r="R49" t="n">
-        <v>6433680</v>
+        <v>6433695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,7 +6379,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121349455</v>
+        <v>121349471</v>
       </c>
       <c r="B50" t="n">
         <v>97046</v>
@@ -6410,7 +6410,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>337917</v>
+        <v>337968</v>
       </c>
       <c r="R50" t="n">
-        <v>6433695</v>
+        <v>6433680</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6267,10 +6267,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349455</v>
+        <v>121349471</v>
       </c>
       <c r="B49" t="n">
-        <v>97046</v>
+        <v>97052</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337917</v>
+        <v>337968</v>
       </c>
       <c r="R49" t="n">
-        <v>6433695</v>
+        <v>6433680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,10 +6379,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121349471</v>
+        <v>121349455</v>
       </c>
       <c r="B50" t="n">
-        <v>97046</v>
+        <v>97052</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>337968</v>
+        <v>337917</v>
       </c>
       <c r="R50" t="n">
-        <v>6433680</v>
+        <v>6433695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6270,7 +6270,7 @@
         <v>121349471</v>
       </c>
       <c r="B49" t="n">
-        <v>97052</v>
+        <v>97053</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>121349455</v>
       </c>
       <c r="B50" t="n">
-        <v>97052</v>
+        <v>97053</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6267,7 +6267,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349471</v>
+        <v>121349455</v>
       </c>
       <c r="B49" t="n">
         <v>97053</v>
@@ -6298,7 +6298,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337968</v>
+        <v>337917</v>
       </c>
       <c r="R49" t="n">
-        <v>6433680</v>
+        <v>6433695</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,7 +6379,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121349455</v>
+        <v>121349471</v>
       </c>
       <c r="B50" t="n">
         <v>97053</v>
@@ -6410,7 +6410,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>337917</v>
+        <v>337968</v>
       </c>
       <c r="R50" t="n">
-        <v>6433695</v>
+        <v>6433680</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6267,7 +6267,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349455</v>
+        <v>121349471</v>
       </c>
       <c r="B49" t="n">
         <v>97053</v>
@@ -6298,7 +6298,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337917</v>
+        <v>337968</v>
       </c>
       <c r="R49" t="n">
-        <v>6433695</v>
+        <v>6433680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,7 +6379,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121349471</v>
+        <v>121349455</v>
       </c>
       <c r="B50" t="n">
         <v>97053</v>
@@ -6410,7 +6410,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>337968</v>
+        <v>337917</v>
       </c>
       <c r="R50" t="n">
-        <v>6433680</v>
+        <v>6433695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
+          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6489,6 +6489,131 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121966411</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57510</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Intakan, Vg</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>338023</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6433700</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 2 ex i meståg.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6494,7 +6494,7 @@
         <v>121966411</v>
       </c>
       <c r="B51" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6267,10 +6267,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121349455</v>
+        <v>121966411</v>
       </c>
       <c r="B49" t="n">
-        <v>97061</v>
+        <v>57518</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6279,45 +6279,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221944</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ale-Mickelsdamm/Intakan, Vg</t>
+          <t>Intakan, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>337917</v>
+        <v>338023</v>
       </c>
       <c r="R49" t="n">
-        <v>6433695</v>
+        <v>6433700</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6341,17 +6345,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 knippen, antagligen äkta lopplummer, nedan mindre häll</t>
+          <t>Minst 2 ex i meståg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6360,259 +6374,21 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>121349471</v>
-      </c>
-      <c r="B50" t="n">
-        <v>97061</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Ale-Mickelsdamm/Intakan, Vg</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>337968</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6433680</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera grupper som växer i ungefärligen samma linje horisontellt antagligen äkta lopplummer, nedan den större hällen om man kommer från norr.</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>121966411</v>
-      </c>
-      <c r="B51" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Intakan, Vg</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>338023</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6433700</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 2 ex i meståg.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6270,7 +6270,7 @@
         <v>121966411</v>
       </c>
       <c r="B49" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -5905,7 +5905,7 @@
         <v>120755880</v>
       </c>
       <c r="B46" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -5920,11 +5920,6 @@
       <c r="E46" t="n">
         <v>100049</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -5905,7 +5905,7 @@
         <v>120755880</v>
       </c>
       <c r="B46" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5919,6 +5919,11 @@
       </c>
       <c r="E46" t="n">
         <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -2790,11 +2790,11 @@
         <v>120259571</v>
       </c>
       <c r="B20" t="n">
-        <v>56304</v>
+        <v>56448</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -2790,7 +2790,7 @@
         <v>120259571</v>
       </c>
       <c r="B20" t="n">
-        <v>56448</v>
+        <v>56451</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -2790,7 +2790,7 @@
         <v>120259571</v>
       </c>
       <c r="B20" t="n">
-        <v>56451</v>
+        <v>56457</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6390,6 +6390,713 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125472290</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57942</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>338483</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6433703</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Befinner sig i skogsbrynet ihop med koltrastar.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125472743</v>
+      </c>
+      <c r="B51" t="n">
+        <v>96729</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>338103</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6433693</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125472869</v>
+      </c>
+      <c r="B52" t="n">
+        <v>96729</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>338073</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6433656</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125472912</v>
+      </c>
+      <c r="B53" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>338470</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6433751</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125472951</v>
+      </c>
+      <c r="B54" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mickelsdamm , Vg</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>338479</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6433734</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125474021</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>338185</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6433735</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6395,7 +6395,7 @@
         <v>125472290</v>
       </c>
       <c r="B50" t="n">
-        <v>57942</v>
+        <v>58060</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>125472743</v>
       </c>
       <c r="B51" t="n">
-        <v>96729</v>
+        <v>96897</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125472869</v>
+        <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>96729</v>
+        <v>95873</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6649,24 +6649,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -6677,10 +6681,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>338073</v>
+        <v>338479</v>
       </c>
       <c r="R52" t="n">
-        <v>6433656</v>
+        <v>6433734</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6713,11 +6717,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6753,7 +6752,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6866,10 +6865,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125472951</v>
+        <v>125472869</v>
       </c>
       <c r="B54" t="n">
-        <v>95705</v>
+        <v>96897</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6882,28 +6881,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338479</v>
+        <v>338073</v>
       </c>
       <c r="R54" t="n">
-        <v>6433734</v>
+        <v>6433656</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6950,6 +6945,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6865,10 +6865,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125472869</v>
+        <v>125474021</v>
       </c>
       <c r="B54" t="n">
-        <v>96897</v>
+        <v>8436</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6881,38 +6881,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mickelsdamm , Vg</t>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338073</v>
+        <v>338185</v>
       </c>
       <c r="R54" t="n">
-        <v>6433656</v>
+        <v>6433735</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6949,7 +6954,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Tuvor med stor revmossa</t>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6961,11 +6966,6 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6982,10 +6982,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125474021</v>
+        <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>8436</v>
+        <v>96897</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6998,43 +6998,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mickelsdamm  Sopekärr , Vg</t>
+          <t>Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338185</v>
+        <v>338073</v>
       </c>
       <c r="R55" t="n">
-        <v>6433735</v>
+        <v>6433656</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7071,7 +7066,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gångar på liggande björklåga vid Sopekärr</t>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7083,6 +7078,11 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6392,10 +6392,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125472290</v>
+        <v>125472869</v>
       </c>
       <c r="B50" t="n">
-        <v>58060</v>
+        <v>96897</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6404,39 +6404,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103001</v>
+        <v>2569</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6444,13 +6436,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>338483</v>
+        <v>338073</v>
       </c>
       <c r="R50" t="n">
-        <v>6433703</v>
+        <v>6433656</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6474,17 +6466,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Befinner sig i skogsbrynet ihop med koltrastar.</t>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6493,6 +6485,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6516,10 +6509,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125472743</v>
+        <v>125474021</v>
       </c>
       <c r="B51" t="n">
-        <v>96897</v>
+        <v>8436</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6532,38 +6525,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mickelsdamm , Vg</t>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338103</v>
+        <v>338185</v>
       </c>
       <c r="R51" t="n">
-        <v>6433693</v>
+        <v>6433735</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6600,7 +6598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tuvor med stor revmossa</t>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6612,11 +6610,6 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6633,10 +6626,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125472951</v>
+        <v>125472290</v>
       </c>
       <c r="B52" t="n">
-        <v>95873</v>
+        <v>58060</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6645,25 +6638,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>103001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6671,9 +6664,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6681,13 +6678,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>338479</v>
+        <v>338483</v>
       </c>
       <c r="R52" t="n">
-        <v>6433734</v>
+        <v>6433703</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6711,12 +6708,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Befinner sig i skogsbrynet ihop med koltrastar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6725,7 +6727,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6749,10 +6750,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125472912</v>
+        <v>125472743</v>
       </c>
       <c r="B53" t="n">
-        <v>95873</v>
+        <v>96897</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6765,28 +6766,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -6797,10 +6794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338470</v>
+        <v>338103</v>
       </c>
       <c r="R53" t="n">
-        <v>6433751</v>
+        <v>6433693</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6833,6 +6830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6865,10 +6867,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125474021</v>
+        <v>125472951</v>
       </c>
       <c r="B54" t="n">
-        <v>8436</v>
+        <v>95873</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6881,43 +6883,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mickelsdamm  Sopekärr , Vg</t>
+          <t>Mickelsdamm , Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338185</v>
+        <v>338479</v>
       </c>
       <c r="R54" t="n">
-        <v>6433735</v>
+        <v>6433734</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6952,11 +6953,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gångar på liggande björklåga vid Sopekärr</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6966,6 +6962,11 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6982,10 +6983,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125472869</v>
+        <v>125472912</v>
       </c>
       <c r="B55" t="n">
-        <v>96897</v>
+        <v>95873</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6998,24 +6999,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -7026,10 +7031,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338073</v>
+        <v>338470</v>
       </c>
       <c r="R55" t="n">
-        <v>6433656</v>
+        <v>6433751</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7062,11 +7067,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tuvor med stor revmossa</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6626,7 +6626,7 @@
         <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125472743</v>
       </c>
       <c r="B54" t="n">
-        <v>96952</v>
+        <v>96959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>96952</v>
+        <v>96959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6395,7 +6395,7 @@
         <v>125472290</v>
       </c>
       <c r="B50" t="n">
-        <v>58078</v>
+        <v>58079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125472743</v>
       </c>
       <c r="B54" t="n">
-        <v>96959</v>
+        <v>96962</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>96959</v>
+        <v>96962</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6626,7 +6626,7 @@
         <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125472743</v>
       </c>
       <c r="B54" t="n">
-        <v>96962</v>
+        <v>96966</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>96962</v>
+        <v>96966</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -6626,7 +6626,7 @@
         <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125472743</v>
       </c>
       <c r="B54" t="n">
-        <v>96966</v>
+        <v>96967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>96966</v>
+        <v>96967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7067,6 +7067,349 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126193133</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>338449</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6433719</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>större yta ca 9 x 4 m. i sumpskog</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126193238</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>338459</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6433704</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126193156</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58508</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>338453</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6433720</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6395,7 +6395,7 @@
         <v>125472290</v>
       </c>
       <c r="B50" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>125472951</v>
       </c>
       <c r="B52" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>125472912</v>
       </c>
       <c r="B53" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>125472743</v>
       </c>
       <c r="B54" t="n">
-        <v>96967</v>
+        <v>96969</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>125472869</v>
       </c>
       <c r="B55" t="n">
-        <v>96967</v>
+        <v>96969</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>126193238</v>
       </c>
       <c r="B57" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>126193156</v>
       </c>
       <c r="B58" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7410,6 +7410,210 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126203036</v>
+      </c>
+      <c r="B59" t="n">
+        <v>95584</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>338481</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126202928</v>
+      </c>
+      <c r="B60" t="n">
+        <v>95584</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>338449</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>126203036</v>
       </c>
       <c r="B59" t="n">
-        <v>95584</v>
+        <v>95586</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>126202928</v>
       </c>
       <c r="B60" t="n">
-        <v>95584</v>
+        <v>95586</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>126203036</v>
       </c>
       <c r="B59" t="n">
-        <v>95586</v>
+        <v>95588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>126202928</v>
       </c>
       <c r="B60" t="n">
-        <v>95586</v>
+        <v>95588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7614,6 +7614,218 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126280433</v>
+      </c>
+      <c r="B61" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>338406</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6433747</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126280430</v>
+      </c>
+      <c r="B62" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>338322</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6433729</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>126193238</v>
       </c>
       <c r="B57" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>126193156</v>
       </c>
       <c r="B58" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>126203036</v>
       </c>
       <c r="B59" t="n">
-        <v>95588</v>
+        <v>95592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>126202928</v>
       </c>
       <c r="B60" t="n">
-        <v>95588</v>
+        <v>95592</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>126280433</v>
       </c>
       <c r="B61" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>126280430</v>
       </c>
       <c r="B62" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>126203036</v>
       </c>
       <c r="B59" t="n">
-        <v>95592</v>
+        <v>95595</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>126202928</v>
       </c>
       <c r="B60" t="n">
-        <v>95592</v>
+        <v>95595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>126280433</v>
       </c>
       <c r="B61" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>126280430</v>
       </c>
       <c r="B62" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7826,6 +7826,115 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126391656</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58297</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>337674</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6433658</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7935,6 +7935,658 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126398365</v>
+      </c>
+      <c r="B64" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>338008</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6433676</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126398382</v>
+      </c>
+      <c r="B65" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>338036</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6433654</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126398378</v>
+      </c>
+      <c r="B66" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>337846</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6433661</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126398359</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>338012</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6433665</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 45 - 50 cm hög i äldre skog</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126398385</v>
+      </c>
+      <c r="B68" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>338031</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6433661</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126398373</v>
+      </c>
+      <c r="B69" t="n">
+        <v>95955</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>337826</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6433635</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Blåmossa växer ihop och täcker en större yta ca 3 x 2 m</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8587,6 +8587,459 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126475340</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>338007</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6433672</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På hällmark i äldre tall / barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126475328</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>338009</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6433681</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126475807</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>337732</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6433633</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska hackspår i barrlåga</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126475899</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>338013</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6433667</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39575-2024 artfynd.xlsx
+++ b/artfynd/A 39575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7072,7 +7072,7 @@
         <v>126193133</v>
       </c>
       <c r="B56" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>126193238</v>
       </c>
       <c r="B57" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>126193156</v>
       </c>
       <c r="B58" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>126203036</v>
       </c>
       <c r="B59" t="n">
-        <v>95595</v>
+        <v>95604</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>126202928</v>
       </c>
       <c r="B60" t="n">
-        <v>95595</v>
+        <v>95604</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>126280433</v>
       </c>
       <c r="B61" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>126280430</v>
       </c>
       <c r="B62" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>126391656</v>
       </c>
       <c r="B63" t="n">
-        <v>58297</v>
+        <v>58300</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>126398365</v>
       </c>
       <c r="B64" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>126398382</v>
       </c>
       <c r="B65" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>126398378</v>
       </c>
       <c r="B66" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>126398359</v>
       </c>
       <c r="B67" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>126398385</v>
       </c>
       <c r="B68" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>126398373</v>
       </c>
       <c r="B69" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126475807</v>
+        <v>126476117</v>
       </c>
       <c r="B72" t="n">
         <v>57654</v>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>337732</v>
+        <v>338031</v>
       </c>
       <c r="R72" t="n">
-        <v>6433633</v>
+        <v>6433671</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8892,17 +8892,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska hackspår i barrlåga</t>
+          <t>Färska hack i barrlåga</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8929,10 +8929,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126475899</v>
+        <v>126476075</v>
       </c>
       <c r="B73" t="n">
-        <v>58027</v>
+        <v>58516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>208249</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8962,17 +8962,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8980,13 +8977,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338013</v>
+        <v>337974</v>
       </c>
       <c r="R73" t="n">
-        <v>6433667</v>
+        <v>6433674</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9010,12 +9007,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9024,6 +9021,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9039,6 +9037,229 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126475807</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>337732</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6433633</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska hackspår i barrlåga</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126475899</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>338013</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6433667</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
